--- a/data/trans_orig/P33B5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023</t>
+          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34439</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>365872</t>
+          <t>367012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>395252</t>
+          <t>395630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272784</t>
+          <t>274048</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>299500</t>
+          <t>300369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654353</t>
+          <t>654647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>691813</t>
+          <t>690989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>31875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>388629</t>
+          <t>387731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408840</t>
+          <t>408598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>468892</t>
+          <t>468183</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>494680</t>
+          <t>494840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>865979</t>
+          <t>864901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>898658</t>
+          <t>898462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>53974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18844</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>38868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>53537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56270</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475559</t>
+          <t>475276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501529</t>
+          <t>501026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452259</t>
+          <t>451989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479345</t>
+          <t>479432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935734</t>
+          <t>936553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>973916</t>
+          <t>972186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43278</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69382</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101556</t>
+          <t>103902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36090</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71369</t>
+          <t>70886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74197</t>
+          <t>74254</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>64312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>134553</t>
+          <t>135431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>770662</t>
+          <t>768197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>854212</t>
+          <t>852212</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>561411</t>
+          <t>562219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>603859</t>
+          <t>603808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1340268</t>
+          <t>1340199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1475236</t>
+          <t>1472990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>56913</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>80066</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>94050</t>
+          <t>93993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127731</t>
+          <t>127323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>41632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54139</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74533</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105037</t>
+          <t>105078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139055</t>
+          <t>139950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>427342</t>
+          <t>427392</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>463696</t>
+          <t>462620</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>358562</t>
+          <t>358294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>390821</t>
+          <t>392224</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>792967</t>
+          <t>797349</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>846147</t>
+          <t>845024</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,49%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>93455</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>115841</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>47299</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>21230</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>36885</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81639</t>
+          <t>79989</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>39360</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>103840</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>281967</t>
+          <t>282382</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>306656</t>
+          <t>306959</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>406219</t>
+          <t>408881</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>553705</t>
+          <t>553997</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>713993</t>
+          <t>715829</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>876045</t>
+          <t>873729</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>31036</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>49149</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>71733</t>
+          <t>72418</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>94562</t>
+          <t>95247</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107806</t>
+          <t>108799</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>139671</t>
+          <t>139872</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>43076</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>60032</t>
+          <t>60237</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>49408</t>
+          <t>49673</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>69544</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>71304</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>95511</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>193435</t>
+          <t>194101</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>217019</t>
+          <t>216950</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>234472</t>
+          <t>236517</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>263601</t>
+          <t>263716</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>435802</t>
+          <t>435203</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>474063</t>
+          <t>474326</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>123270</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>187737</t>
+          <t>187787</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>244754</t>
+          <t>248519</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>338972</t>
+          <t>341741</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>399422</t>
+          <t>399588</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>511220</t>
+          <t>511483</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>77600</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>99883</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>143353</t>
+          <t>144928</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>154757</t>
+          <t>158306</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>211162</t>
+          <t>211646</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>166367</t>
+          <t>159730</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>243133</t>
+          <t>242285</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>241716</t>
+          <t>251989</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>339918</t>
+          <t>339486</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>447701</t>
+          <t>445817</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>562403</t>
+          <t>569715</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2978480</t>
+          <t>2979668</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3120159</t>
+          <t>3127077</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2860246</t>
+          <t>2856529</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3076003</t>
+          <t>3061141</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5862816</t>
+          <t>5868661</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6093833</t>
+          <t>6120779</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>385795</t>
+          <t>394805</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367012</t>
+          <t>377926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>395630</t>
+          <t>403487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289991</t>
+          <t>337971</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274048</t>
+          <t>322068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300369</t>
+          <t>348600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>675786</t>
+          <t>732776</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654647</t>
+          <t>711707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>690989</t>
+          <t>747111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>44957</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50412</t>
+          <t>60989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>400340</t>
+          <t>447534</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>387731</t>
+          <t>434615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408598</t>
+          <t>457807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>482013</t>
+          <t>464660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>468183</t>
+          <t>450061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>494840</t>
+          <t>475165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>882354</t>
+          <t>912195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>864901</t>
+          <t>892984</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>898462</t>
+          <t>927267</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25984</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35361</t>
+          <t>40361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>42043</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30790</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>60959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1976,27 +1976,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>23519</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53537</t>
+          <t>59194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>69415</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56355</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84199</t>
+          <t>91777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>489237</t>
+          <t>570799</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475276</t>
+          <t>554083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501026</t>
+          <t>582878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>466163</t>
+          <t>535031</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451989</t>
+          <t>519371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479432</t>
+          <t>548786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>955400</t>
+          <t>1105830</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936553</t>
+          <t>1084735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>972186</t>
+          <t>1126028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>42953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37604</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69839</t>
+          <t>63338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>77464</t>
+          <t>79887</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103902</t>
+          <t>96906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>28095</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36071</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70886</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61762</t>
+          <t>67675</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48886</t>
+          <t>56003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74254</t>
+          <t>80023</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>106983</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>99843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135431</t>
+          <t>137842</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>808256</t>
+          <t>613531</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>768197</t>
+          <t>592507</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>852212</t>
+          <t>629012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>582576</t>
+          <t>598104</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562219</t>
+          <t>580054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>603808</t>
+          <t>613282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1390834</t>
+          <t>1211635</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1340199</t>
+          <t>1184760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1472990</t>
+          <t>1236430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>68461</t>
+          <t>78037</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56913</t>
+          <t>65711</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>109295</t>
+          <t>121335</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93993</t>
+          <t>104096</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>140145</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>52985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>46301</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>58133</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>49124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>78580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>63856</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>82740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>121990</t>
+          <t>131578</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105078</t>
+          <t>114011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139950</t>
+          <t>151876</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>446248</t>
+          <t>487381</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>427392</t>
+          <t>465810</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>462620</t>
+          <t>506138</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>417830</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>358294</t>
+          <t>399945</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>392224</t>
+          <t>435173</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>821588</t>
+          <t>905210</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>797349</t>
+          <t>876827</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>845024</t>
+          <t>930140</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>31576</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>40994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>58933</t>
+          <t>65195</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93455</t>
+          <t>76394</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>87310</t>
+          <t>96771</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>111815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>34619</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47299</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>55060</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>46244</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>66166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>78914</t>
+          <t>86824</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>74127</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103840</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>295340</t>
+          <t>326568</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>282382</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>306959</t>
+          <t>339917</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>479760</t>
+          <t>297977</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>408881</t>
+          <t>284000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>553997</t>
+          <t>312651</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>775100</t>
+          <t>624545</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>715829</t>
+          <t>603552</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>873729</t>
+          <t>643494</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>39408</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>54370</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>91215</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>72418</t>
+          <t>79631</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>95247</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>122153</t>
+          <t>134889</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>108799</t>
+          <t>120017</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>139872</t>
+          <t>151740</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34998</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>27111</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>55167</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>44783</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>60237</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>34625</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>62613</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>49673</t>
+          <t>53377</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>69544</t>
+          <t>73406</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>81357</t>
+          <t>88482</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>101220</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>224447</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>194101</t>
+          <t>210472</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>216950</t>
+          <t>237189</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>249010</t>
+          <t>271225</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>236517</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>263716</t>
+          <t>287950</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>455032</t>
+          <t>495672</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>435203</t>
+          <t>475113</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>474326</t>
+          <t>514960</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>158650</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>123287</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>187787</t>
+          <t>200672</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>303951</t>
+          <t>333149</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>248519</t>
+          <t>304805</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>341741</t>
+          <t>362646</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>462601</t>
+          <t>505681</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>399588</t>
+          <t>467921</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>511483</t>
+          <t>542602</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43843</t>
+          <t>50914</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>86033</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>141087</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>123120</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>144928</t>
+          <t>160415</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>183945</t>
+          <t>206131</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158306</t>
+          <t>183263</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>211646</t>
+          <t>232034</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>228051</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>159730</t>
+          <t>198538</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>242285</t>
+          <t>256728</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>305795</t>
+          <t>335839</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>251989</t>
+          <t>306691</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>364410</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>513430</t>
+          <t>563889</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>445817</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>606382</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3031240</t>
+          <t>3065066</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2979668</t>
+          <t>3023622</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3127077</t>
+          <t>3107793</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2924853</t>
+          <t>2922798</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2856529</t>
+          <t>2879798</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3061141</t>
+          <t>2963406</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>5956093</t>
+          <t>5987863</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5868661</t>
+          <t>5926044</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6120779</t>
+          <t>6042201</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
